--- a/assets/dungeon_paths.xlsx
+++ b/assets/dungeon_paths.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="副本路径配置" sheetId="1" r:id="R3a61702fc4064726"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="难度映射" sheetId="2" r:id="Rf694b006e61f4017"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="副本路径配置" sheetId="1" r:id="R52c84897bf0b4c3a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="难度映射" sheetId="2" r:id="Ra9736f947a8c4182"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -456,7 +456,7 @@
         <x:v>[[2,2],[5,2],[8,2],[11,2],[14,2],[18,2],[21,2],[24,2],[27,2],[31,2],[35,2],[39,2],[43,2],[47,2],[50,2],[54,2],[58,2],[62,2],[66,2]]</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
-        <x:v>[[-681.182,580],[-362.894,580],[-285.287,584.312],[-220.614,583.45],[-220.614,583.45],[-148.181,577.414],[-70.574,570.515],[9.62,556.718],[84.64,550.682],[157.073,536.885],[219.159,525.675],[278.658,496.357],[330.396,454.104],[361.439,391.156],[356.265,323.034],[312.288,260.086],[260.55,212.659],[182.943,175.58],[110.51,195.413],[61.359,254.049],[51.011,317.859],[51.011,372.184],[87.227,434.27],[162.247,442.03],[232.093,412.712],[250.201,362.699],[201.05,299.751],[157.073,257.498],[102.748,223.006],[35.489,180.753],[-62.813,161.782],[-158.528,158.333],[-230.961,180.753],[-305.981,229.042],[-334.437,303.2],[-331.85,382.532],[-282.699,435.995],[-223.2,468.762],[-143.006,480.834],[-67.986,467.037],[-42.117,393.741],[-42.117,325.619],[-75.747,274.744],[-135.246,232.491],[-197.332,182.478],[-241.309,129.878],[-285.286,66.93],[-321.503,-1.192],[-342.198,-74.488],[-313.742,-145.197],[-256.83,-213.319],[-174.049,-229.703],[-106.79,-204.696],[-67.986,-158.994],[-34.356,-105.531],[-29.182,-36.547],[-67.986,23.814],[-117.137,50.546],[-174.049,50.546],[-220.613,0.533],[-228.374,-62.415],[-186.984,-107.255],[-135.246,-159.855],[-67.987,-196.934],[1.859,-223.665],[87.227,-232.288],[149.312,-239.187],[219.159,-234.875],[276.071,-212.455],[314.875,-161.579],[335.57,-95.182],[332.983,-33.959],[314.875,22.091],[268.311,57.445],[198.465,79.865],[126.032,66.068],[87.228,3.12],[87.228,-59.828],[128.618,-109.841],[190.704,-167.615],[252.79,-235.737],[284.684,-286.055],[257.554,-330],[-286.029,-330],[-323.4,-380],[-287.727,-430],[308.515,-430],[340.79,-480],[310.214,-530],[97.877,-516.977],[72.397,-536.229],[48.615,-593.418]]</x:v>
+        <x:v>[[0,580],[318.288,580],[395.895,584.312],[460.568,583.45],[460.568,583.45],[533.001,577.414],[610.608,570.515],[690.802,556.718],[765.822,550.682],[838.255,536.885],[900.341,525.675],[959.84,496.357],[1011.578,454.104],[1042.621,391.156],[1037.447,323.034],[993.47,260.086],[941.732,212.659],[864.125,175.58],[791.692,195.413],[742.541,254.049],[732.193,317.859],[732.193,372.184],[768.409,434.27],[843.429,442.03],[913.275,412.712],[931.383,362.699],[882.232,299.751],[838.255,257.498],[783.93,223.006],[716.671,180.753],[618.369,161.782],[522.654,158.333],[450.221,180.753],[375.201,229.042],[346.745,303.2],[349.332,382.532],[398.483,435.995],[457.982,468.762],[538.176,480.834],[613.196,467.037],[639.065,393.741],[639.065,325.619],[605.435,274.744],[545.936,232.491],[483.85,182.478],[439.873,129.878],[395.896,66.93],[359.679,-1.192],[338.984,-74.488],[367.44,-145.197],[424.352,-213.319],[507.133,-229.703],[574.392,-204.696],[613.196,-158.994],[646.826,-105.531],[652,-36.547],[613.196,23.814],[564.045,50.546],[507.133,50.546],[460.569,0.533],[452.808,-62.415],[494.198,-107.255],[545.936,-159.855],[613.195,-196.934],[683.041,-223.665],[768.409,-232.288],[830.494,-239.187],[900.341,-234.875],[957.253,-212.455],[996.057,-161.579],[1016.752,-95.182],[1014.165,-33.959],[996.057,22.091],[949.493,57.445],[879.647,79.865],[807.214,66.068],[768.41,3.12],[768.41,-59.828],[809.8,-109.841],[871.886,-167.615],[933.972,-235.737],[965.866,-286.055],[938.736,-330],[395.153,-330],[357.782,-380],[393.455,-430],[989.697,-430],[1021.972,-480],[991.396,-530],[779.059,-516.977],[753.579,-536.229],[729.797,-593.418]]</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="28" customHeight="1">
@@ -467,7 +467,7 @@
         <x:v>[[2,2],[5,2],[8,2],[11,2],[14,2],[18,2],[21,2],[24,2],[27,2],[31,2],[35,2],[39,2],[43,2],[47,2],[50,2],[54,2],[58,2],[62,2],[66,2]]</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>[[-700,630],[-356.479,630],[-318.872,605.373],[-300,570],[-300,200],[-250,150],[-200,200],[-200,580],[-150,630],[-100,580],[-100,200],[-50,150],[0,200],[0,580],[50,630],[100,580],[100,580],[100,200],[150,150],[200,200],[200,580],[250,630],[300,580],[300,150],[261.625,100.881],[191.016,50],[-213.452,50],[-294.806,27.743],[-330,-36.726],[-330,-400],[-312.348,-426.862],[-268,-450],[268,-450],[301.769,-433.115],[330,-400],[330,-110.656],[303.138,-69.212],[268,-50],[-161.027,-50],[-196.332,-65.35],[-230,-91.445],[-230,-300.203],[-215.418,-330.903],[-180.113,-350],[195.958,-350],[219.75,-332.348],[238.937,-297.539],[238.937,-219.254],[199.795,-163.228],[164.491,-150],[-111.038,-150],[-141.738,-163.048],[-157.088,-200.655],[-124.086,-250],[-64.99,-257.675],[0,-273.792],[30.7,-316.004],[56.795,-362.821],[29.933,-423.453],[-8.442,-465.665],[-9.977,-512.482],[11.001,-560.947]]</x:v>
+        <x:v>[[0,630],[343.521,630],[381.128,605.373],[400,570],[400,200],[450,150],[500,200],[500,580],[550,630],[600,580],[600,200],[650,150],[700,200],[700,580],[750,630],[800,580],[800,580],[800,200],[850,150],[900,200],[900,580],[950,630],[1000,580],[1000,150],[961.625,100.881],[891.016,50],[486.548,50],[405.194,27.743],[370,-36.726],[370,-400],[387.652,-426.862],[432,-450],[968,-450],[1001.769,-433.115],[1030,-400],[1030,-110.656],[1003.138,-69.212],[968,-50],[538.973,-50],[503.668,-65.35],[470,-91.445],[470,-300.203],[484.582,-330.903],[519.887,-350],[895.958,-350],[919.75,-332.348],[938.937,-297.539],[938.937,-219.254],[899.795,-163.228],[864.491,-150],[588.962,-150],[558.262,-163.048],[542.912,-200.655],[575.914,-250],[635.01,-257.675],[700,-273.792],[730.7,-316.004],[756.795,-362.821],[729.933,-423.453],[691.558,-465.665],[690.023,-512.482],[711.001,-560.947]]</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="28" customHeight="1">
@@ -478,7 +478,7 @@
         <x:v>[[2,2],[5,2],[8,2],[11,2],[14,2],[18,2],[21,2],[24,2],[27,2],[31,2],[35,2],[39,2],[43,2],[47,2],[50,2],[54,2],[58,2],[62,2],[66,2]]</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
-        <x:v>[[-645.448,1100],[-366.001,631.782],[-222.568,700.201],[-49.46,736.238],[111.677,731.373],[276.983,692.325],[418.872,621.744],[527.683,536.838],[634.021,419.784],[708.21,282.121],[745.305,155.175],[755.197,13.391],[740.359,-146.528],[695.845,-284.19],[616.71,-402.893],[515.318,-531.488],[384.25,-618.867],[230.925,-676.57],[85.019,-697.178],[-75.725,-683.164],[-229.05,-634.529],[-370.01,-543.853],[-476.348,-435.866],[-550.537,-317.987],[-595.051,-187.743],[-622.254,-48.431],[-604.943,85.11],[-557.956,254.921],[-468.929,382.692],[-352.699,500.571],[-226.577,564.044],[-88.09,605.26],[70.181,609.382],[203.722,581.355],[334.79,530.247],[455.966,430.503],[547.466,330.759],[614.236,184.853],[629.074,35.65],[621.655,-111.08],[579.614,-242.972],[512.843,-342.716],[411.451,-442.46],[300.167,-522.42],[156.734,-566.109],[-6.483,-578.474],[-174.646,-524.893],[-295.822,-446.582],[-387.322,-355.906],[-456.566,-245.446],[-491.188,-100.364],[-493.661,27.407],[-461.512,157.651],[-399.687,282.949],[-290.876,395.882],[-137.551,474.193],[38.031,498.099],[218.559,460.18],[342.208,375.274],[446.073,275.53],[498.006,151.057],[515.317,-10.511],[478.222,-167.133],[386.722,-316.336],[248.235,-418.553],[62.761,-458.945],[-147.443,-405.364],[-278.511,-299.85],[-360.119,-174.552],[-382.376,-4.741],[-340.335,147.76],[-253.781,260.693],[-140.024,339.004],[13.301,374.45],[166.626,347.247],[295.221,262.341],[371.883,152.705],[391.667,18.34],[369.41,-118.498],[285.329,-242.971],[149.315,-322.931],[-38.632,-328.701],[-159.808,-253.688],[-243.889,-140.755],[-261.2,-13.808],[-229.051,111.49],[-140.024,206.288],[-8.956,259.869],[129.531,236.788],[228.45,156.828],[272.964,49.665],[253.18,-79.754],[161.68,-192.687],[5.882,-210.822],[-112.821,-122.619],[-137.551,-2.267],[-85.618,102.423],[20.72,142.815],[122.112,100.773],[146.842,48.016],[141.896,-32.768],[97.382,-105.309],[35.557,-50.079]]</x:v>
+        <x:v>[[0,1100],[279.447,631.782],[422.88,700.201],[595.988,736.238],[757.125,731.373],[922.431,692.325],[1064.32,621.744],[1173.131,536.838],[1279.469,419.784],[1353.658,282.121],[1390.753,155.175],[1400.645,13.391],[1385.807,-146.528],[1341.293,-284.19],[1262.158,-402.893],[1160.766,-531.488],[1029.698,-618.867],[876.373,-676.57],[730.467,-697.178],[569.723,-683.164],[416.398,-634.529],[275.438,-543.853],[169.1,-435.866],[94.911,-317.987],[50.397,-187.743],[23.194,-48.431],[40.505,85.11],[87.492,254.921],[176.519,382.692],[292.749,500.571],[418.871,564.044],[557.358,605.26],[715.629,609.382],[849.17,581.355],[980.238,530.247],[1101.414,430.503],[1192.914,330.759],[1259.684,184.853],[1274.522,35.65],[1267.103,-111.08],[1225.062,-242.972],[1158.291,-342.716],[1056.899,-442.46],[945.615,-522.42],[802.182,-566.109],[638.965,-578.474],[470.802,-524.893],[349.626,-446.582],[258.126,-355.906],[188.882,-245.446],[154.26,-100.364],[151.787,27.407],[183.936,157.651],[245.761,282.949],[354.572,395.882],[507.897,474.193],[683.479,498.099],[864.007,460.18],[987.656,375.274],[1091.521,275.53],[1143.454,151.057],[1160.765,-10.511],[1123.67,-167.133],[1032.17,-316.336],[893.683,-418.553],[708.209,-458.945],[498.005,-405.364],[366.937,-299.85],[285.329,-174.552],[263.072,-4.741],[305.113,147.76],[391.667,260.693],[505.424,339.004],[658.749,374.45],[812.074,347.247],[940.669,262.341],[1017.331,152.705],[1037.115,18.34],[1014.858,-118.498],[930.777,-242.971],[794.763,-322.931],[606.816,-328.701],[485.64,-253.688],[401.559,-140.755],[384.248,-13.808],[416.397,111.49],[505.424,206.288],[636.492,259.869],[774.979,236.788],[873.898,156.828],[918.412,49.665],[898.628,-79.754],[807.128,-192.687],[651.33,-210.822],[532.627,-122.619],[507.897,-2.267],[559.83,102.423],[666.168,142.815],[767.56,100.773],[792.29,48.016],[787.344,-32.768],[742.83,-105.309],[681.005,-50.079]]</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="28" customHeight="1">
@@ -489,7 +489,7 @@
         <x:v>[[2,2],[5,2],[8,2],[11,2],[14,2],[18,2],[21,2],[24,2],[27,2],[31,2],[35,2],[39,2],[43,2],[47,2],[50,2],[54,2],[58,2],[62,2],[66,2]]</x:v>
       </x:c>
       <x:c r="C6" s="11" t="str">
-        <x:v>[[-550,50],[-474.625,135.027],[-369.561,202.123],[-200,260],[-264.226,309.631],[-328.828,351.777],[-365.984,408.893],[-400.103,480.709],[-385.132,558.057],[-321.613,583.332],[-253.975,543.41],[-190,500],[-136.164,547.859],[-76.012,594.994],[0,630],[79.496,596.678],[134.659,541.515],[190,500],[237.677,544.641],[280.364,559.341],[338.022,526.634],[373.224,468.976],[354.076,401.068],[319.144,340.914],[262.028,293.237],[207.677,260],[-200,260],[-550,260],[-550,-450],[-474.625,-364.97300000000007],[-369.561,-297.87700000000007],[-200,-240],[-264.226,-190.36900000000003],[-328.828,-148.22300000000007],[-365.984,-91.10700000000008],[-400.103,-19.291000000000054],[-385.132,58.0569999999999],[-321.613,83.332],[-253.975,43.40999999999997],[-190,1.1368683772161603e-13],[-136.164,47.85900000000004],[-76.012,94.99400000000003],[0,130.0000000000001],[79.49599999999998,96.678],[134.659,41.514999999999986],[190,1.1368683772161603e-13],[237.67700000000002,44.64099999999996],[280.36400000000003,59.34100000000001],[338.02199999999993,26.63400000000013],[373.22399999999993,-31.024],[354.076,-98.93200000000013],[319.144,-159.086],[262.028,-206.76300000000003],[207.67700000000002,-240],[-200,-240],[-550,-240],[-454.916,-282.687],[-369.812,-342.84],[-309.659,-400.498],[-249.506,-440.69],[-186.858,-396.049],[-129.2,-368.874],[-54.077,-356.669],[8.571,-354.445],[76.479,-362.472],[151.602,-380.208],[211.755,-402.935],[266.918,-445.622],[332.061,-418.447],[379.738,-376.301],[437.396,-339.145],[500,-284.794],[500,-97.933],[0,-97.933],[0,-205.493],[0,-308.062],[0,-430.592],[0,-530.666],[0,-588.324]]</x:v>
+        <x:v>[[0,50],[75.375,135.027],[180.439,202.123],[350,260],[285.774,309.631],[221.172,351.777],[184.016,408.893],[149.897,480.709],[164.868,558.057],[228.387,583.332],[296.025,543.41],[360,500],[413.836,547.859],[473.988,594.994],[550,630],[629.496,596.678],[684.659,541.515],[740,500],[787.677,544.641],[830.364,559.341],[888.022,526.634],[923.224,468.976],[904.076,401.068],[869.144,340.914],[812.028,293.237],[757.677,260],[350,260],[0,260],[0,-450],[75.375,-364.97300000000007],[180.439,-297.87700000000007],[350,-240],[285.774,-190.36900000000003],[221.172,-148.22300000000007],[184.016,-91.10700000000008],[149.897,-19.291000000000054],[164.868,58.0569999999999],[228.387,83.332],[296.025,43.40999999999997],[360,1.1368683772161603e-13],[413.836,47.85900000000004],[473.988,94.99400000000003],[550,130.0000000000001],[629.496,96.678],[684.659,41.514999999999986],[740,1.1368683772161603e-13],[787.677,44.64099999999996],[830.364,59.34100000000001],[888.022,26.63400000000013],[923.224,-31.024],[904.076,-98.93200000000013],[869.144,-159.086],[812.028,-206.76300000000003],[757.677,-240],[350,-240],[0,-240],[95.084,-282.687],[180.188,-342.84],[240.341,-400.498],[300.494,-440.69],[363.142,-396.049],[420.8,-368.874],[495.923,-356.669],[558.571,-354.445],[626.479,-362.472],[701.602,-380.208],[761.755,-402.935],[816.918,-445.622],[882.061,-418.447],[929.738,-376.301],[987.396,-339.145],[1050,-284.794],[1050,-97.933],[550,-97.933],[550,-205.493],[550,-308.062],[550,-430.592],[550,-530.666],[550,-588.324]]</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="28" customHeight="1">
@@ -500,7 +500,7 @@
         <x:v>[[2,2],[5,2],[8,2],[11,2],[14,2],[18,2],[21,2],[24,2],[27,2],[31,2],[35,2],[39,2],[43,2],[47,2],[50,2],[54,2],[58,2],[62,2],[66,2]]</x:v>
       </x:c>
       <x:c r="C7" s="11" t="str">
-        <x:v>[[-620,480],[-444.643,480],[0,480],[-165,630],[-330,480],[-165,330],[0,480],[165,630],[330,480],[165,330],[0,480],[330,480],[330,180],[165,330],[0,180],[165,30],[330,180],[0,180],[-165,30],[-330,180],[-165,330],[0,180],[-330,180],[-330,-120],[-165,30],[0,-120],[-165,-270],[-330,-120],[0,-120],[165,-270],[330,-120],[165,30],[0,-120],[330,-120],[330,-420],[165,-270],[0,-420],[-165,-270],[-330,-420],[501.118,-420],[501.118,-270],[0,-270],[0,-335.158],[0,-420.281],[0,-507.9],[0,-583.041]]</x:v>
+        <x:v>[[0,480],[175.357,480],[620,480],[455,630],[290,480],[455,330],[620,480],[785,630],[950,480],[785,330],[620,480],[950,480],[950,180],[785,330],[620,180],[785,30],[950,180],[620,180],[455,30],[290,180],[455,330],[620,180],[290,180],[290,-120],[455,30],[620,-120],[455,-270],[290,-120],[620,-120],[785,-270],[950,-120],[785,30],[620,-120],[950,-120],[950,-420],[785,-270],[620,-420],[455,-270],[290,-420],[1121.118,-420],[1121.118,-270],[620,-270],[620,-335.158],[620,-420.281],[620,-507.9],[620,-583.041]]</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="28" customHeight="1">
@@ -511,7 +511,7 @@
         <x:v>[[2,2],[5,2],[8,2],[11,2],[14,2],[18,2],[21,2],[24,2],[27,2],[31,2],[35,2],[39,2],[43,2],[47,2],[50,2],[54,2],[58,2],[62,2],[66,2]]</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
-        <x:v>[[-600,530.0000000000001],[-100.00000000000006,530.0000000000001],[-67.86500000000001,552.6470000000003],[-40,590.0000000000001],[-64.78800000000001,631.0790000000001],[-100.00000000000006,650.0000000000001],[-143.216,632.1230000000002],[-160.00000000000003,590.0000000000001],[-144.41600000000003,557.3260000000004],[-100.00000000000006,530.0000000000001],[100,530.0000000000001],[134.07999999999998,552.919],[160,590.0000000000001],[136.10799999999995,632.245],[100,650.0000000000001],[61.25999999999999,634.7360000000002],[39.99999999999994,590.0000000000001],[52.60899999999998,552.8000000000001],[100,530.0000000000001],[500.00000000000006,530.0000000000001],[500.00000000000006,280.0000000000001],[0,280.0000000000001],[65.74199999999996,299.37700000000007],[115.12700000000001,329.43600000000004],[155.73799999999994,385.0190000000001],[160,450.0000000000001],[102.24599999999998,407.4230000000001],[50.714999999999975,390.24700000000007],[0,380],[-75.33200000000002,385.9760000000001],[-122.66100000000003,413.65700000000015],[-160.00000000000003,450.0000000000001],[-149.472,376.32500000000005],[-104.565,324.3280000000001],[-55.18000000000001,289.97300000000007],[0,280.0000000000001],[-500.0000000000001,280.0000000000001],[-500.0000000000001,30.000000000000114],[-100.00000000000006,30.000000000000114],[-67.86500000000001,52.647000000000276],[-40,90.00000000000011],[-64.78800000000001,131.07900000000006],[-100.00000000000006,150.0000000000001],[-143.216,132.12299999999993],[-160.00000000000009,90.00000000000011],[-144.41600000000008,57.326000000000136],[-100.00000000000006,30.000000000000114],[100,30.000000000000114],[134.07999999999998,52.919000000000096],[160,90.00000000000011],[136.10799999999995,132.24500000000012],[100,150.0000000000001],[61.25999999999999,134.7360000000001],[39.99999999999994,90.00000000000011],[52.608999999999924,52.800000000000296],[100,30.000000000000114],[500.00000000000006,30.000000000000114],[500.00000000000006,-219.99999999999983],[0,-219.99999999999983],[65.7419999999999,-200.62299999999988],[115.12700000000001,-170.5639999999999],[155.73799999999994,-114.981],[160,-49.999999999999886],[102.24599999999998,-92.57699999999966],[50.714999999999975,-109.7529999999997],[0,-119.99999999999983],[-75.33200000000002,-114.02399999999977],[-122.66100000000006,-86.34299999999996],[-160.00000000000009,-49.999999999999886],[-149.472,-123.67499999999984],[-104.565,-175.67199999999997],[-55.180000000000064,-210.02699999999976],[0,-219.99999999999983],[-500.00000000000017,-219.99999999999983],[-500.00000000000017,-469.9999999999998],[-200.00000000000003,-469.9999999999998],[-135.76700000000002,-429.66999999999996],[-80.00000000000003,-371.92999999999995],[-103.83200000000002,-307.98099999999994],[-174.87200000000004,-323.4769999999999],[-200.00000000000003,-370],[-249.66000000000003,-322.846],[-318.55100000000004,-310.429],[-320.00000000000006,-372.696],[-275.001,-430.90199999999993],[-200.00000000000003,-470],[200.00000000000006,-470],[264.233,-429.66999999999996],[319.99999999999994,-371.92999999999984],[296.16799999999995,-307.9809999999998],[225.128,-323.4769999999998],[199.99999999999994,-370],[150.33999999999997,-322.846],[81.44899999999996,-310.429],[79.99999999999994,-372.696],[124.99900000000002,-430.9019999999997],[199.99999999999994,-470],[500.00000000000006,-470],[500.00000000000006,-470],[500.00000000000006,-219.99999999999994],[0,-219.99999999999994],[0,-319.99999999999994],[0,-419.99999999999994],[0,-520],[0,-599.9999999999999]]</x:v>
+        <x:v>[[0,530.0000000000001],[500,530.0000000000001],[532.135,552.6470000000003],[560,590.0000000000001],[535.212,631.0790000000001],[500,650.0000000000001],[456.784,632.1230000000002],[440,590.0000000000001],[455.584,557.3260000000004],[500,530.0000000000001],[700,530.0000000000001],[734.08,552.919],[760,590.0000000000001],[736.108,632.245],[700,650.0000000000001],[661.26,634.7360000000002],[640,590.0000000000001],[652.609,552.8000000000001],[700,530.0000000000001],[1100,530.0000000000001],[1100,280.0000000000001],[600,280.0000000000001],[665.742,299.37700000000007],[715.127,329.43600000000004],[755.738,385.0190000000001],[760,450.0000000000001],[702.246,407.4230000000001],[650.715,390.24700000000007],[600,380],[524.668,385.9760000000001],[477.339,413.65700000000015],[440,450.0000000000001],[450.528,376.32500000000005],[495.435,324.3280000000001],[544.82,289.97300000000007],[600,280.0000000000001],[100,280.0000000000001],[100,30.000000000000114],[500,30.000000000000114],[532.135,52.647000000000276],[560,90.00000000000011],[535.212,131.07900000000006],[500,150.0000000000001],[456.784,132.12299999999993],[440,90.00000000000011],[455.584,57.326000000000136],[500,30.000000000000114],[700,30.000000000000114],[734.08,52.919000000000096],[760,90.00000000000011],[736.108,132.24500000000012],[700,150.0000000000001],[661.26,134.7360000000001],[640,90.00000000000011],[652.609,52.800000000000296],[700,30.000000000000114],[1100,30.000000000000114],[1100,-219.99999999999983],[600,-219.99999999999983],[665.742,-200.62299999999988],[715.127,-170.5639999999999],[755.738,-114.981],[760,-49.999999999999886],[702.246,-92.57699999999966],[650.715,-109.7529999999997],[600,-119.99999999999983],[524.668,-114.02399999999977],[477.339,-86.34299999999996],[440,-49.999999999999886],[450.528,-123.67499999999984],[495.435,-175.67199999999997],[544.82,-210.02699999999976],[600,-219.99999999999983],[100,-219.99999999999983],[100,-469.9999999999998],[400,-469.9999999999998],[464.233,-429.66999999999996],[520,-371.92999999999995],[496.168,-307.98099999999994],[425.128,-323.4769999999999],[400,-370],[350.34,-322.846],[281.449,-310.429],[280,-372.696],[324.999,-430.90199999999993],[400,-470],[800,-470],[864.233,-429.66999999999996],[920,-371.92999999999984],[896.168,-307.9809999999998],[825.128,-323.4769999999998],[800,-370],[750.34,-322.846],[681.449,-310.429],[680,-372.696],[724.999,-430.9019999999997],[800,-470],[1100,-470],[1100,-470],[1100,-219.99999999999994],[600,-219.99999999999994],[600,-319.99999999999994],[600,-419.99999999999994],[600,-520],[600,-599.9999999999999]]</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="28" customHeight="1">
@@ -522,7 +522,7 @@
         <x:v>[[2,2],[5,2],[8,2],[11,2],[14,2],[18,2],[21,2],[24,2],[27,2],[31,2],[35,2],[39,2],[43,2],[47,2],[50,2],[54,2],[58,2],[62,2],[66,2]]</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
-        <x:v>[[-500,380],[-318,380],[-321.079,462.949],[-281.365,543.012],[-222.487,606.915],[-155.945,644.823],[-89.402,621.413],[-26.692,594.171],[0,540],[26.692000000000007,594.1710000000002],[89.40199999999999,621.4130000000004],[155.94500000000005,644.8230000000002],[222.48700000000002,606.9150000000003],[281.36499999999995,543.0119999999998],[321.079,462.9490000000002],[318,380],[293.204,318.15099999999995],[241.44099999999997,261.5120000000003],[188.16699999999997,204.7750000000002],[120.77099999999996,164],[56.58600000000001,128.187],[0,100.00000000000023],[-56.58600000000001,128.187],[-120.77099999999996,164],[-188.167,204.77500000000032],[-241.44100000000003,261.5120000000003],[-293.204,318.15099999999995],[-318,380],[-130.318,380],[-72.981,447.485],[9.6,218.69],[93.469,522.538],[153.16,380],[318,380],[500,380],[500,-300],[318.00000000000017,-300],[321.079,-217.05099999999976],[281.36499999999995,-136.98800000000017],[222.48700000000002,-73.08499999999992],[155.94500000000005,-35.17699999999979],[89.40199999999999,-58.586999999999875],[26.692000000000007,-85.82899999999978],[0,-140.0000000000001],[-26.692000000000064,-85.82899999999978],[-89.40199999999999,-58.58699999999942],[-155.94500000000008,-35.17699999999979],[-222.48700000000002,-73.08499999999941],[-281.36499999999995,-136.98800000000017],[-321.079,-217.05099999999976],[-318.0000000000001,-300],[-293.204,-361.84900000000005],[-241.44100000000003,-418.4879999999997],[-188.167,-475.2249999999997],[-120.77099999999996,-516],[-56.58600000000001,-551.813],[0,-579.9999999999997],[56.58600000000001,-551.813],[120.77099999999996,-516],[188.1670000000001,-475.2249999999997],[241.44099999999997,-418.4879999999997],[293.204,-361.84900000000005],[318.00000000000017,-300],[130.31799999999998,-300],[72.98099999999994,-232.51499999999976],[-9.599999999999966,-461.30999999999995],[-93.469,-157.46199999999988],[-153.16,-300],[-318.0000000000001,-300],[-500,-300],[-500,0],[-408.478,70.393],[-322.612,104.022],[-248.058,83.92],[-176.332,69.473],[-110.262,43.715],[-55.503,20.784]]</x:v>
+        <x:v>[[0,380],[182,380],[178.921,462.949],[218.635,543.012],[277.513,606.915],[344.055,644.823],[410.598,621.413],[473.308,594.171],[500,540],[526.692,594.1710000000002],[589.402,621.4130000000004],[655.945,644.8230000000002],[722.487,606.9150000000003],[781.365,543.0119999999998],[821.079,462.9490000000002],[818,380],[793.204,318.15099999999995],[741.441,261.5120000000003],[688.167,204.7750000000002],[620.771,164],[556.586,128.187],[500,100.00000000000023],[443.414,128.187],[379.229,164],[311.833,204.77500000000032],[258.559,261.5120000000003],[206.796,318.15099999999995],[182,380],[369.682,380],[427.019,447.485],[509.6,218.69],[593.469,522.538],[653.16,380],[818,380],[1000,380],[1000,-300],[818,-300],[821.079,-217.05099999999976],[781.365,-136.98800000000017],[722.487,-73.08499999999992],[655.945,-35.17699999999979],[589.402,-58.586999999999875],[526.692,-85.82899999999978],[500,-140.0000000000001],[473.308,-85.82899999999978],[410.598,-58.58699999999942],[344.055,-35.17699999999979],[277.513,-73.08499999999941],[218.635,-136.98800000000017],[178.921,-217.05099999999976],[182,-300],[206.796,-361.84900000000005],[258.559,-418.4879999999997],[311.833,-475.2249999999997],[379.229,-516],[443.414,-551.813],[500,-579.9999999999997],[556.586,-551.813],[620.771,-516],[688.167,-475.2249999999997],[741.441,-418.4879999999997],[793.204,-361.84900000000005],[818,-300],[630.318,-300],[572.981,-232.51499999999976],[490.4,-461.30999999999995],[406.531,-157.46199999999988],[346.84,-300],[182,-300],[0,-300],[0,0],[91.522,70.393],[177.388,104.022],[251.942,83.92],[323.668,69.473],[389.738,43.715],[444.497,20.784]]</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="28" customHeight="1">
@@ -533,7 +533,7 @@
         <x:v>[[2,2],[5,2],[8,2],[11,2],[14,2],[18,2],[21,2],[24,2],[27,2],[31,2],[35,2],[39,2],[43,2],[47,2],[50,2],[54,2],[58,2],[62,2],[66,2]]</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
-        <x:v>[[-200,850],[-200,630],[-50,630],[-50,530],[-200,530],[-200,430],[-50,430],[50,430],[200,430],[200,530],[50,530],[50,630],[200,630],[450,630],[450,330],[340,330],[-340,330],[-170,160],[0,330],[170,160],[340,330],[340,160],[-340,160],[-170,-10],[0,160],[170,-10],[340,160],[340,-10],[-340,-10],[-170,-180],[0,-10],[170,-180],[340,-10],[340,-180],[-340,-180],[-170,-350],[0,-180],[170,-350],[340,-180],[340,-480],[170,-350],[0,-480],[-170,-350],[-340,-480],[-340,-350],[0,-350],[0,-400],[0,-450],[0,-500],[0,-550]]</x:v>
+        <x:v>[[0,850],[0,630],[150,630],[150,530],[0,530],[0,430],[150,430],[250,430],[400,430],[400,530],[250,530],[250,630],[400,630],[650,630],[650,330],[540,330],[-140,330],[30,160],[200,330],[370,160],[540,330],[540,160],[-140,160],[30,-10],[200,160],[370,-10],[540,160],[540,-10],[-140,-10],[30,-180],[200,-10],[370,-180],[540,-10],[540,-180],[-140,-180],[30,-350],[200,-180],[370,-350],[540,-180],[540,-480],[370,-350],[200,-480],[30,-350],[-140,-480],[-140,-350],[200,-350],[200,-400],[200,-450],[200,-500],[200,-550]]</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="28" customHeight="1">
@@ -550,7 +550,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra763d1ceb53448c8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1ee833f63073449a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -688,7 +688,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc93745219a5f4f8e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f26cb625fa640e9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/assets/dungeon_paths.xlsx
+++ b/assets/dungeon_paths.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="副本路径配置" sheetId="1" r:id="R52c84897bf0b4c3a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="难度映射" sheetId="2" r:id="Ra9736f947a8c4182"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="副本路径配置" sheetId="1" r:id="R0c87ac272db84d5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="难度映射" sheetId="2" r:id="R4576e56d70414bb2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -445,7 +445,7 @@
         <x:v>[[2,2],[5,2],[8,2],[11,2],[14,2],[18,2],[21,2],[24,2],[27,2],[31,2],[35,2],[39,2],[43,2],[47,2],[50,2],[54,2],[58,2],[62,2],[66,2]]</x:v>
       </x:c>
       <x:c r="C2" s="11" t="str">
-        <x:v>[[0,1000],[0,330],[-25.869,304.994],[-77.607,306.718],[-100,330],[-100,380.014],[-68.958,417.092],[0,430],[33.63,415.341],[75.02,385.161],[100,330],[87.066,289.472],[53.436,254.118],[0,230],[-62.086,221.378],[-124.171,236.037],[-173.323,269.667],[-200,330],[-197.413,398.122],[-184.478,441.237],[-153.435,481.765],[-114.631,509.358],[-57.719,526.604],[0,530],[43.977,518.79],[80.193,509.305],[129.345,477.4],[160.388,437.734],[186.257,392.895],[200,330],[200,276.538],[176.718,228.249],[143.089,198.93],[104.286,169.613],[49.961,148.917],[0,130],[-62.086,129.138],[-121.585,136.036],[-181.084,152.42],[-235.409,190.361],[-269.039,231.751],[-292.321,276.591],[-300,330],[-305.174,390.361],[-294.826,454.171],[-287.065,499.872],[-245.674,547.298],[-204.284,577.478],[-147.373,607.659],[-82.7,627.491],[0,630],[59.499,621.377],[116.411,602.406],[173.323,573.088],[214.713,533.422],[250.93,478.235],[274.212,435.982],[284.559,384.244],[300,330],[289.652,264.465],[261.196,198.93],[206.871,135.982],[142.198,85.969],[72.352,56.651],[0,30],[-280,30],[-330,-20],[-280,-70],[280,-70],[330,-120],[280,-170],[-280,-170],[-330,-220],[-280,-270],[280,-270],[330,-320],[280,-370],[-270,-370],[-330,-420],[-280,-470],[-120.526,-470],[-65.521,-505.053],[-26.483,-574.352]]</x:v>
+        <x:v>[[241.787,922.065],[241.787,287.667],[223.297,263.99],[186.319,265.622],[170.315,287.667],[170.315,335.023],[192.501,370.131],[241.787,382.353],[265.823,368.473],[295.405,339.897],[313.258,287.667],[304.014,249.293],[279.978,215.817],[241.787,192.981],[197.412,184.817],[153.039,198.697],[117.909,230.54],[98.843,287.667],[100.692,352.169],[109.936,392.993],[132.123,431.368],[159.857,457.494],[200.534,473.824],[241.787,477.04],[273.218,466.425],[299.102,457.444],[334.232,427.235],[356.419,389.676],[374.908,347.22],[384.73,287.667],[384.73,237.046],[368.09,191.323],[344.055,163.562],[316.322,135.803],[277.495,116.206],[241.787,98.295],[197.412,97.478],[154.887,104.01],[112.362,119.523],[73.535,155.448],[49.499,194.639],[32.859,237.096],[27.371,287.667],[23.673,344.821],[31.069,405.24],[36.615,448.513],[66.198,493.418],[95.781,521.995],[136.456,550.572],[182.679,569.35],[241.787,571.726],[284.312,563.561],[324.988,545.598],[365.664,517.838],[395.246,480.28],[421.131,428.025],[437.771,388.017],[445.166,339.029],[456.202,287.667],[448.806,225.614],[428.468,163.562],[389.641,103.959],[343.418,56.603],[293.498,28.843],[241.787,3.608],[41.665,3.608],[5.929,-43.735],[41.665,-91.078],[441.908,-91.078],[477.644,-138.421],[441.908,-185.764],[41.665,-185.764],[5.929,-233.107],[41.665,-280.45],[441.908,-280.45],[477.644,-327.794],[441.908,-375.137],[48.812,-375.137],[5.929,-422.48],[41.665,-469.823],[155.644,-469.823],[194.957,-503.013],[222.859,-568.63]]</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="28" customHeight="1">
@@ -456,7 +456,7 @@
         <x:v>[[2,2],[5,2],[8,2],[11,2],[14,2],[18,2],[21,2],[24,2],[27,2],[31,2],[35,2],[39,2],[43,2],[47,2],[50,2],[54,2],[58,2],[62,2],[66,2]]</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
-        <x:v>[[0,580],[318.288,580],[395.895,584.312],[460.568,583.45],[460.568,583.45],[533.001,577.414],[610.608,570.515],[690.802,556.718],[765.822,550.682],[838.255,536.885],[900.341,525.675],[959.84,496.357],[1011.578,454.104],[1042.621,391.156],[1037.447,323.034],[993.47,260.086],[941.732,212.659],[864.125,175.58],[791.692,195.413],[742.541,254.049],[732.193,317.859],[732.193,372.184],[768.409,434.27],[843.429,442.03],[913.275,412.712],[931.383,362.699],[882.232,299.751],[838.255,257.498],[783.93,223.006],[716.671,180.753],[618.369,161.782],[522.654,158.333],[450.221,180.753],[375.201,229.042],[346.745,303.2],[349.332,382.532],[398.483,435.995],[457.982,468.762],[538.176,480.834],[613.196,467.037],[639.065,393.741],[639.065,325.619],[605.435,274.744],[545.936,232.491],[483.85,182.478],[439.873,129.878],[395.896,66.93],[359.679,-1.192],[338.984,-74.488],[367.44,-145.197],[424.352,-213.319],[507.133,-229.703],[574.392,-204.696],[613.196,-158.994],[646.826,-105.531],[652,-36.547],[613.196,23.814],[564.045,50.546],[507.133,50.546],[460.569,0.533],[452.808,-62.415],[494.198,-107.255],[545.936,-159.855],[613.195,-196.934],[683.041,-223.665],[768.409,-232.288],[830.494,-239.187],[900.341,-234.875],[957.253,-212.455],[996.057,-161.579],[1016.752,-95.182],[1014.165,-33.959],[996.057,22.091],[949.493,57.445],[879.647,79.865],[807.214,66.068],[768.41,3.12],[768.41,-59.828],[809.8,-109.841],[871.886,-167.615],[933.972,-235.737],[965.866,-286.055],[938.736,-330],[395.153,-330],[357.782,-380],[393.455,-430],[989.697,-430],[1021.972,-480],[991.396,-530],[779.059,-516.977],[753.579,-536.229],[729.797,-593.418]]</x:v>
+        <x:v>[[-165.832,589.55],[-46.93,591.687],[11.817,595.999],[60.773,595.137],[60.773,595.137],[115.604,589.101],[174.351,582.202],[235.057,568.405],[291.846,562.369],[346.676,548.572],[393.674,537.362],[438.714,508.044],[477.879,465.791],[501.378,402.843],[497.461,334.721],[464.171,271.773],[425.007,224.346],[366.259,187.267],[311.429,207.1],[274.222,265.736],[266.389,329.546],[266.389,383.871],[293.804,445.957],[350.593,453.717],[403.465,424.399],[417.173,374.386],[379.966,311.438],[346.676,269.185],[305.553,234.693],[254.639,192.44],[180.226,173.469],[107.771,170.02],[52.941,192.44],[-3.848,240.729],[-25.389,314.887],[-23.43,394.219],[13.776,447.682],[58.816,480.449],[119.521,492.521],[176.31,478.724],[195.893,405.428],[195.893,337.306],[170.435,286.431],[125.396,244.178],[78.397,194.165],[45.108,141.565],[11.818,78.617],[-15.598,10.495],[-31.264,-62.801],[-9.723,-133.51],[33.358,-201.632],[96.022,-218.016],[146.936,-193.009],[176.31,-147.307],[201.768,-93.844],[205.684,-24.86],[176.31,35.501],[139.104,62.233],[96.022,62.233],[60.774,12.22],[54.899,-50.728],[86.231,-95.568],[125.396,-148.168],[176.31,-185.247],[229.182,-211.978],[293.804,-220.601],[340.801,-227.5],[393.674,-223.188],[436.756,-200.768],[466.13,-149.892],[481.796,-83.495],[479.837,-22.272],[466.13,33.778],[430.882,69.132],[378.009,91.552],[323.179,77.755],[293.805,14.807],[293.805,-48.141],[325.136,-98.154],[372.134,-155.928],[419.132,-224.05],[443.276,-274.368],[422.739,-318.313],[11.255,-318.313],[-17.034,-368.313],[9.97,-418.313],[461.315,-418.313],[485.747,-468.313],[462.602,-518.313],[301.866,-505.29],[282.578,-524.542],[264.575,-581.731]]</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="28" customHeight="1">
@@ -467,7 +467,7 @@
         <x:v>[[2,2],[5,2],[8,2],[11,2],[14,2],[18,2],[21,2],[24,2],[27,2],[31,2],[35,2],[39,2],[43,2],[47,2],[50,2],[54,2],[58,2],[62,2],[66,2]]</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>[[0,630],[343.521,630],[381.128,605.373],[400,570],[400,200],[450,150],[500,200],[500,580],[550,630],[600,580],[600,200],[650,150],[700,200],[700,580],[750,630],[800,580],[800,580],[800,200],[850,150],[900,200],[900,580],[950,630],[1000,580],[1000,150],[961.625,100.881],[891.016,50],[486.548,50],[405.194,27.743],[370,-36.726],[370,-400],[387.652,-426.862],[432,-450],[968,-450],[1001.769,-433.115],[1030,-400],[1030,-110.656],[1003.138,-69.212],[968,-50],[538.973,-50],[503.668,-65.35],[470,-91.445],[470,-300.203],[484.582,-330.903],[519.887,-350],[895.958,-350],[919.75,-332.348],[938.937,-297.539],[938.937,-219.254],[899.795,-163.228],[864.491,-150],[588.962,-150],[558.262,-163.048],[542.912,-200.655],[575.914,-250],[635.01,-257.675],[700,-273.792],[730.7,-316.004],[756.795,-362.821],[729.933,-423.453],[691.558,-465.665],[690.023,-512.482],[711.001,-560.947]]</x:v>
+        <x:v>[[-262.039,602.876],[-19.69,602.876],[6.841,579.247],[20.155,545.306],[20.155,190.293],[55.429,142.319],[90.704,190.293],[90.704,554.901],[125.977,602.876],[161.251,554.901],[161.251,190.293],[196.526,142.319],[231.8,190.293],[231.8,554.901],[267.075,602.876],[302.349,554.901],[302.349,554.901],[302.349,190.293],[337.623,142.319],[372.897,190.293],[372.897,554.901],[408.171,602.876],[443.445,554.901],[443.445,142.319],[416.372,95.189],[366.559,46.369],[81.213,46.369],[23.819,25.014],[-1.01,-36.844],[-1.01,-385.403],[11.443,-411.177],[42.73,-433.378],[420.87,-433.378],[444.693,-417.177],[464.61,-385.403],[464.61,-107.779],[445.659,-68.014],[420.87,-49.58],[118.198,-49.58],[93.291,-64.308],[69.539,-89.346],[69.539,-289.649],[79.826,-319.105],[104.733,-337.429],[370.045,-337.429],[386.831,-320.492],[400.367,-287.092],[400.367,-211.978],[372.752,-158.222],[347.846,-145.53],[153.464,-145.53],[131.806,-158.049],[120.977,-194.133],[144.259,-241.479],[185.95,-248.843],[231.8,-264.307],[253.459,-304.81],[271.868,-349.73],[252.917,-407.906],[225.844,-448.408],[224.762,-493.329],[239.562,-539.831]]</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="28" customHeight="1">
@@ -478,7 +478,7 @@
         <x:v>[[2,2],[5,2],[8,2],[11,2],[14,2],[18,2],[21,2],[24,2],[27,2],[31,2],[35,2],[39,2],[43,2],[47,2],[50,2],[54,2],[58,2],[62,2],[66,2]]</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
-        <x:v>[[0,1100],[279.447,631.782],[422.88,700.201],[595.988,736.238],[757.125,731.373],[922.431,692.325],[1064.32,621.744],[1173.131,536.838],[1279.469,419.784],[1353.658,282.121],[1390.753,155.175],[1400.645,13.391],[1385.807,-146.528],[1341.293,-284.19],[1262.158,-402.893],[1160.766,-531.488],[1029.698,-618.867],[876.373,-676.57],[730.467,-697.178],[569.723,-683.164],[416.398,-634.529],[275.438,-543.853],[169.1,-435.866],[94.911,-317.987],[50.397,-187.743],[23.194,-48.431],[40.505,85.11],[87.492,254.921],[176.519,382.692],[292.749,500.571],[418.871,564.044],[557.358,605.26],[715.629,609.382],[849.17,581.355],[980.238,530.247],[1101.414,430.503],[1192.914,330.759],[1259.684,184.853],[1274.522,35.65],[1267.103,-111.08],[1225.062,-242.972],[1158.291,-342.716],[1056.899,-442.46],[945.615,-522.42],[802.182,-566.109],[638.965,-578.474],[470.802,-524.893],[349.626,-446.582],[258.126,-355.906],[188.882,-245.446],[154.26,-100.364],[151.787,27.407],[183.936,157.651],[245.761,282.949],[354.572,395.882],[507.897,474.193],[683.479,498.099],[864.007,460.18],[987.656,375.274],[1091.521,275.53],[1143.454,151.057],[1160.765,-10.511],[1123.67,-167.133],[1032.17,-316.336],[893.683,-418.553],[708.209,-458.945],[498.005,-405.364],[366.937,-299.85],[285.329,-174.552],[263.072,-4.741],[305.113,147.76],[391.667,260.693],[505.424,339.004],[658.749,374.45],[812.074,347.247],[940.669,262.341],[1017.331,152.705],[1037.115,18.34],[1014.858,-118.498],[930.777,-242.971],[794.763,-322.931],[606.816,-328.701],[485.64,-253.688],[401.559,-140.755],[384.248,-13.808],[416.397,111.49],[505.424,206.288],[636.492,259.869],[774.979,236.788],[873.898,156.828],[918.412,49.665],[898.628,-79.754],[807.128,-192.687],[651.33,-210.822],[532.627,-122.619],[507.897,-2.267],[559.83,102.423],[666.168,142.815],[767.56,100.773],[792.29,48.016],[787.344,-32.768],[742.83,-105.309],[681.005,-50.079]]</x:v>
+        <x:v>[[-656.771,1112.106],[-377.324,643.888],[-233.891,712.307],[-60.783,748.344],[100.354,743.479],[265.66,704.431],[407.549,633.85],[516.36,548.944],[622.698,431.89],[696.887,294.227],[733.982,167.281],[743.874,25.497],[729.036,-134.422],[684.522,-272.084],[605.387,-390.787],[503.995,-519.382],[372.927,-606.761],[219.602,-664.464],[73.696,-685.072],[-87.048,-671.058],[-240.373,-622.423],[-381.333,-531.747],[-487.671,-423.76],[-561.86,-305.881],[-606.374,-175.637],[-633.577,-36.325],[-616.266,97.216],[-569.279,267.027],[-480.252,394.798],[-364.022,512.677],[-237.9,576.15],[-99.413,617.366],[58.858,621.488],[192.399,593.461],[323.467,542.353],[444.643,442.609],[536.143,342.865],[602.913,196.959],[617.751,47.756],[610.332,-98.974],[568.291,-230.866],[501.52,-330.61],[400.128,-430.354],[288.844,-510.314],[145.411,-554.003],[-17.806,-566.368],[-185.969,-512.787],[-307.145,-434.476],[-398.645,-343.8],[-467.889,-233.34],[-502.511,-88.258],[-504.984,39.513],[-472.835,169.757],[-411.01,295.055],[-302.199,407.988],[-148.874,486.299],[26.708,510.205],[207.236,472.286],[330.885,387.38],[434.75,287.636],[486.683,163.163],[503.994,1.595],[466.899,-155.027],[375.399,-304.23],[236.912,-406.447],[51.438,-446.839],[-158.766,-393.258],[-289.834,-287.744],[-371.442,-162.446],[-393.699,7.365],[-351.658,159.866],[-265.104,272.799],[-151.347,351.11],[1.978,386.556],[155.303,359.353],[283.898,274.447],[360.56,164.811],[380.344,30.446],[358.087,-106.392],[274.006,-230.865],[137.992,-310.825],[-49.955,-316.595],[-171.131,-241.582],[-255.212,-128.649],[-272.523,-1.702],[-240.374,123.596],[-151.347,218.394],[-20.279,271.975],[118.208,248.894],[217.127,168.934],[261.641,61.771],[241.857,-67.648],[150.357,-180.581],[-5.441,-198.716],[-124.144,-110.513],[-148.874,9.839],[-96.941,114.529],[9.397,154.921],[110.789,112.879],[135.519,60.122],[130.573,-20.662],[86.059,-93.203],[24.234,-37.973]]</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="28" customHeight="1">
@@ -489,7 +489,7 @@
         <x:v>[[2,2],[5,2],[8,2],[11,2],[14,2],[18,2],[21,2],[24,2],[27,2],[31,2],[35,2],[39,2],[43,2],[47,2],[50,2],[54,2],[58,2],[62,2],[66,2]]</x:v>
       </x:c>
       <x:c r="C6" s="11" t="str">
-        <x:v>[[0,50],[75.375,135.027],[180.439,202.123],[350,260],[285.774,309.631],[221.172,351.777],[184.016,408.893],[149.897,480.709],[164.868,558.057],[228.387,583.332],[296.025,543.41],[360,500],[413.836,547.859],[473.988,594.994],[550,630],[629.496,596.678],[684.659,541.515],[740,500],[787.677,544.641],[830.364,559.341],[888.022,526.634],[923.224,468.976],[904.076,401.068],[869.144,340.914],[812.028,293.237],[757.677,260],[350,260],[0,260],[0,-450],[75.375,-364.97300000000007],[180.439,-297.87700000000007],[350,-240],[285.774,-190.36900000000003],[221.172,-148.22300000000007],[184.016,-91.10700000000008],[149.897,-19.291000000000054],[164.868,58.0569999999999],[228.387,83.332],[296.025,43.40999999999997],[360,1.1368683772161603e-13],[413.836,47.85900000000004],[473.988,94.99400000000003],[550,130.0000000000001],[629.496,96.678],[684.659,41.514999999999986],[740,1.1368683772161603e-13],[787.677,44.64099999999996],[830.364,59.34100000000001],[888.022,26.63400000000013],[923.224,-31.024],[904.076,-98.93200000000013],[869.144,-159.086],[812.028,-206.76300000000003],[757.677,-240],[350,-240],[0,-240],[95.084,-282.687],[180.188,-342.84],[240.341,-400.498],[300.494,-440.69],[363.142,-396.049],[420.8,-368.874],[495.923,-356.669],[558.571,-354.445],[626.479,-362.472],[701.602,-380.208],[761.755,-402.935],[816.918,-445.622],[882.061,-418.447],[929.738,-376.301],[987.396,-339.145],[1050,-284.794],[1050,-97.933],[550,-97.933],[550,-205.493],[550,-308.062],[550,-430.592],[550,-530.666],[550,-588.324]]</x:v>
+        <x:v>[[1.519,710.776],[0.437,259.091],[108.901,263.567],[180.804,258.736],[145.438,306.255],[109.866,346.608],[89.406,401.294],[70.618,470.055],[78.863,544.113],[113.839,568.312],[151.083,530.089],[186.309,488.525],[215.955,534.348],[249.076,579.478],[290.932,612.995],[334.705,581.091],[365.08,528.274],[395.553,488.525],[421.806,531.267],[445.311,545.342],[477.06,514.026],[496.444,458.821],[485.9,393.802],[466.666,336.207],[435.214,290.559],[405.287,258.736],[180.804,258.736],[-11.921,258.736],[-11.921,-421.06],[29.584,-339.65],[87.435,-275.408],[180.804,-219.993],[145.438,-172.474],[109.866,-132.121],[89.406,-77.435],[70.618,-8.674],[78.863,65.384],[113.839,89.583],[151.083,51.36],[186.309,9.796],[215.955,55.619],[249.076,100.749],[290.932,134.266],[334.705,102.362],[365.08,49.545],[395.553,9.796],[421.806,52.538],[445.311,66.613],[477.06,35.297],[496.444,-19.908],[485.9,-84.927],[466.666,-142.522],[435.214,-188.17],[405.287,-219.993],[180.804,-219.993],[-11.921,-219.993],[40.437,-260.864],[87.298,-318.458],[120.421,-373.664],[153.543,-412.146],[188.04,-369.404],[219.789,-343.385],[261.155,-331.699],[295.652,-329.57],[333.044,-337.255],[374.41,-354.237],[407.533,-375.997],[437.907,-416.868],[473.778,-390.849],[500.031,-350.496],[531.78,-314.921],[566.252,-262.882],[566.252,-83.97],[290.932,-83.97],[290.932,-186.954],[290.932,-285.16],[290.932,-402.477],[290.932,-498.294],[290.932,-553.499]]</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="28" customHeight="1">
@@ -500,7 +500,7 @@
         <x:v>[[2,2],[5,2],[8,2],[11,2],[14,2],[18,2],[21,2],[24,2],[27,2],[31,2],[35,2],[39,2],[43,2],[47,2],[50,2],[54,2],[58,2],[62,2],[66,2]]</x:v>
       </x:c>
       <x:c r="C7" s="11" t="str">
-        <x:v>[[0,480],[175.357,480],[620,480],[455,630],[290,480],[455,330],[620,480],[785,630],[950,480],[785,330],[620,480],[950,480],[950,180],[785,330],[620,180],[785,30],[950,180],[620,180],[455,30],[290,180],[455,330],[620,180],[290,180],[290,-120],[455,30],[620,-120],[455,-270],[290,-120],[620,-120],[785,-270],[950,-120],[785,30],[620,-120],[950,-120],[950,-420],[785,-270],[620,-420],[455,-270],[290,-420],[1121.118,-420],[1121.118,-270],[620,-270],[620,-335.158],[620,-420.281],[620,-507.9],[620,-583.041]]</x:v>
+        <x:v>[[7.469,742.297],[9.079,499.783],[223.277,497.879],[113.92,644.417],[4.563,497.879],[113.92,351.342],[223.277,497.879],[332.635,644.417],[441.992,497.879],[332.635,351.342],[223.277,497.879],[441.992,497.879],[441.992,204.804],[332.635,351.342],[223.277,204.804],[332.635,58.266],[441.992,204.804],[223.277,204.804],[113.92,58.266],[4.563,204.804],[113.92,351.342],[223.277,204.804],[4.563,204.804],[4.563,-88.271],[113.92,58.266],[223.277,-88.271],[113.92,-234.809],[4.563,-88.271],[223.277,-88.271],[332.635,-234.809],[441.992,-88.271],[332.635,58.266],[223.277,-88.271],[441.992,-88.271],[441.992,-381.346],[332.635,-234.809],[223.277,-381.346],[113.92,-234.809],[4.563,-381.346],[555.404,-381.346],[555.404,-234.809],[223.277,-234.809],[223.277,-298.463],[223.277,-381.621],[223.277,-467.217],[223.277,-540.624]]</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="28" customHeight="1">
@@ -511,7 +511,7 @@
         <x:v>[[2,2],[5,2],[8,2],[11,2],[14,2],[18,2],[21,2],[24,2],[27,2],[31,2],[35,2],[39,2],[43,2],[47,2],[50,2],[54,2],[58,2],[62,2],[66,2]]</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
-        <x:v>[[0,530.0000000000001],[500,530.0000000000001],[532.135,552.6470000000003],[560,590.0000000000001],[535.212,631.0790000000001],[500,650.0000000000001],[456.784,632.1230000000002],[440,590.0000000000001],[455.584,557.3260000000004],[500,530.0000000000001],[700,530.0000000000001],[734.08,552.919],[760,590.0000000000001],[736.108,632.245],[700,650.0000000000001],[661.26,634.7360000000002],[640,590.0000000000001],[652.609,552.8000000000001],[700,530.0000000000001],[1100,530.0000000000001],[1100,280.0000000000001],[600,280.0000000000001],[665.742,299.37700000000007],[715.127,329.43600000000004],[755.738,385.0190000000001],[760,450.0000000000001],[702.246,407.4230000000001],[650.715,390.24700000000007],[600,380],[524.668,385.9760000000001],[477.339,413.65700000000015],[440,450.0000000000001],[450.528,376.32500000000005],[495.435,324.3280000000001],[544.82,289.97300000000007],[600,280.0000000000001],[100,280.0000000000001],[100,30.000000000000114],[500,30.000000000000114],[532.135,52.647000000000276],[560,90.00000000000011],[535.212,131.07900000000006],[500,150.0000000000001],[456.784,132.12299999999993],[440,90.00000000000011],[455.584,57.326000000000136],[500,30.000000000000114],[700,30.000000000000114],[734.08,52.919000000000096],[760,90.00000000000011],[736.108,132.24500000000012],[700,150.0000000000001],[661.26,134.7360000000001],[640,90.00000000000011],[652.609,52.800000000000296],[700,30.000000000000114],[1100,30.000000000000114],[1100,-219.99999999999983],[600,-219.99999999999983],[665.742,-200.62299999999988],[715.127,-170.5639999999999],[755.738,-114.981],[760,-49.999999999999886],[702.246,-92.57699999999966],[650.715,-109.7529999999997],[600,-119.99999999999983],[524.668,-114.02399999999977],[477.339,-86.34299999999996],[440,-49.999999999999886],[450.528,-123.67499999999984],[495.435,-175.67199999999997],[544.82,-210.02699999999976],[600,-219.99999999999983],[100,-219.99999999999983],[100,-469.9999999999998],[400,-469.9999999999998],[464.233,-429.66999999999996],[520,-371.92999999999995],[496.168,-307.98099999999994],[425.128,-323.4769999999999],[400,-370],[350.34,-322.846],[281.449,-310.429],[280,-372.696],[324.999,-430.90199999999993],[400,-470],[800,-470],[864.233,-429.66999999999996],[920,-371.92999999999984],[896.168,-307.9809999999998],[825.128,-323.4769999999998],[800,-370],[750.34,-322.846],[681.449,-310.429],[680,-372.696],[724.999,-430.9019999999997],[800,-470],[1100,-470],[1100,-470],[1100,-219.99999999999994],[600,-219.99999999999994],[600,-319.99999999999994],[600,-419.99999999999994],[600,-520],[600,-599.9999999999999]]</x:v>
+        <x:v>[[-70.562,510.684],[199.518,505.079],[220.825,525.816],[239.3,560.019],[222.865,597.633],[199.518,614.958],[170.865,598.589],[159.736,560.019],[170.069,530.1],[199.518,505.079],[332.125,505.079],[354.722,526.065],[371.908,560.019],[356.066,598.701],[332.125,614.958],[306.439,600.981],[292.343,560.019],[300.704,525.956],[332.125,505.079],[597.339,505.079],[597.339,276.165],[265.822,276.165],[309.411,293.908],[342.154,321.432],[369.081,372.327],[371.908,431.827],[333.614,392.841],[299.448,377.114],[265.822,367.731],[215.874,373.203],[184.494,398.549],[159.736,431.827],[166.717,364.366],[196.492,316.754],[229.235,285.297],[265.822,276.165],[-4.258,281.77],[-4.258,52.856],[199.518,47.251],[220.825,67.988],[239.3,102.191],[222.865,139.805],[199.518,157.13],[170.865,140.761],[159.736,102.191],[170.069,72.272],[199.518,47.251],[332.125,47.251],[354.722,68.237],[371.908,102.191],[356.066,140.873],[332.125,157.13],[306.439,143.153],[292.343,102.191],[300.704,68.128],[332.125,47.251],[597.339,47.251],[597.339,-181.663],[265.822,-181.663],[309.411,-163.92],[342.154,-136.396],[369.081,-85.501],[371.908,-26.001],[333.614,-64.987],[299.448,-80.714],[265.822,-90.097],[215.874,-84.625],[184.494,-59.279],[159.736,-26.001],[166.717,-93.462],[196.492,-141.074],[229.235,-172.531],[265.822,-181.663],[-4.258,-176.058],[-4.258,-404.972],[133.215,-410.577],[175.803,-373.648],[212.779,-320.778],[196.977,-262.223],[149.875,-276.412],[133.215,-319.011],[100.289,-275.834],[54.611,-264.465],[53.65,-321.48],[83.486,-374.776],[133.215,-410.577],[398.429,-410.577],[441.018,-373.648],[477.992,-320.778],[462.192,-262.223],[415.089,-276.412],[398.429,-319.011],[365.502,-275.834],[319.826,-264.465],[318.865,-321.48],[348.701,-374.776],[398.429,-410.577],[597.339,-410.577],[597.339,-410.577],[597.339,-181.663],[265.822,-181.663],[265.822,-273.228],[265.822,-364.794],[265.822,-456.36],[265.822,-529.612]]</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="28" customHeight="1">
@@ -522,7 +522,7 @@
         <x:v>[[2,2],[5,2],[8,2],[11,2],[14,2],[18,2],[21,2],[24,2],[27,2],[31,2],[35,2],[39,2],[43,2],[47,2],[50,2],[54,2],[58,2],[62,2],[66,2]]</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
-        <x:v>[[0,380],[182,380],[178.921,462.949],[218.635,543.012],[277.513,606.915],[344.055,644.823],[410.598,621.413],[473.308,594.171],[500,540],[526.692,594.1710000000002],[589.402,621.4130000000004],[655.945,644.8230000000002],[722.487,606.9150000000003],[781.365,543.0119999999998],[821.079,462.9490000000002],[818,380],[793.204,318.15099999999995],[741.441,261.5120000000003],[688.167,204.7750000000002],[620.771,164],[556.586,128.187],[500,100.00000000000023],[443.414,128.187],[379.229,164],[311.833,204.77500000000032],[258.559,261.5120000000003],[206.796,318.15099999999995],[182,380],[369.682,380],[427.019,447.485],[509.6,218.69],[593.469,522.538],[653.16,380],[818,380],[1000,380],[1000,-300],[818,-300],[821.079,-217.05099999999976],[781.365,-136.98800000000017],[722.487,-73.08499999999992],[655.945,-35.17699999999979],[589.402,-58.586999999999875],[526.692,-85.82899999999978],[500,-140.0000000000001],[473.308,-85.82899999999978],[410.598,-58.58699999999942],[344.055,-35.17699999999979],[277.513,-73.08499999999941],[218.635,-136.98800000000017],[178.921,-217.05099999999976],[182,-300],[206.796,-361.84900000000005],[258.559,-418.4879999999997],[311.833,-475.2249999999997],[379.229,-516],[443.414,-551.813],[500,-579.9999999999997],[556.586,-551.813],[620.771,-516],[688.167,-475.2249999999997],[741.441,-418.4879999999997],[793.204,-361.84900000000005],[818,-300],[630.318,-300],[572.981,-232.51499999999976],[490.4,-461.30999999999995],[406.531,-157.46199999999988],[346.84,-300],[182,-300],[0,-300],[0,0],[91.522,70.393],[177.388,104.022],[251.942,83.92],[323.668,69.473],[389.738,43.715],[444.497,20.784]]</x:v>
+        <x:v>[[-2.806,339.94],[101.08,339.94],[99.322,415.741],[121.991,488.904],[155.599,547.301],[193.581,581.942],[231.564,560.549],[267.359,535.655],[282.595,486.152],[297.831,535.655],[333.626,560.549],[371.609,581.942],[409.591,547.301],[443.199,488.904],[465.868,415.741],[464.11,339.94],[449.956,283.421],[420.41,231.662],[390.001,179.815],[351.531,142.553],[314.894,109.827],[282.595,84.069],[250.296,109.827],[213.659,142.553],[175.189,179.815],[144.78,231.662],[115.234,283.421],[101.08,339.94],[208.209,339.94],[240.937,401.609],[288.075,192.531],[335.947,470.195],[370.019,339.94],[464.11,339.94],[567.996,339.94],[567.996,-281.462],[464.11,-281.462],[465.868,-205.661],[443.199,-132.497],[409.591,-74.101],[371.609,-39.46],[333.626,-60.852],[297.831,-85.747],[282.595,-135.25],[267.359,-85.747],[231.564,-60.852],[193.581,-39.46],[155.599,-74.101],[121.991,-132.497],[99.322,-205.661],[101.08,-281.462],[115.234,-337.981],[144.78,-389.739],[175.189,-441.587],[213.659,-478.848],[250.296,-511.575],[282.595,-537.333],[314.894,-511.575],[351.531,-478.848],[390.001,-441.587],[420.41,-389.739],[449.956,-337.981],[464.11,-281.462],[356.981,-281.462],[324.253,-219.792],[277.115,-428.871],[229.243,-151.207],[195.171,-281.462],[101.08,-281.462],[-2.806,-281.462],[-2.806,-7.314],[49.435,57.013],[98.447,87.744],[141.003,69.374],[181.944,56.172],[219.657,32.634],[250.914,11.679],[265.935,-23.952],[282.119,-601.402]]</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="28" customHeight="1">
@@ -533,7 +533,7 @@
         <x:v>[[2,2],[5,2],[8,2],[11,2],[14,2],[18,2],[21,2],[24,2],[27,2],[31,2],[35,2],[39,2],[43,2],[47,2],[50,2],[54,2],[58,2],[62,2],[66,2]]</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
-        <x:v>[[0,850],[0,630],[150,630],[150,530],[0,530],[0,430],[150,430],[250,430],[400,430],[400,530],[250,530],[250,630],[400,630],[650,630],[650,330],[540,330],[-140,330],[30,160],[200,330],[370,160],[540,330],[540,160],[-140,160],[30,-10],[200,160],[370,-10],[540,160],[540,-10],[-140,-10],[30,-180],[200,-10],[370,-180],[540,-10],[540,-180],[-140,-180],[30,-350],[200,-180],[370,-350],[540,-180],[540,-480],[370,-350],[200,-480],[30,-350],[-140,-480],[-140,-350],[200,-350],[200,-400],[200,-450],[200,-500],[200,-550]]</x:v>
+        <x:v>[[97.666,812.909],[97.666,597.982],[199.282,597.982],[199.282,500.288],[97.666,500.288],[97.666,402.594],[199.282,402.594],[267.027,402.594],[368.643,402.594],[368.643,500.288],[267.027,500.288],[267.027,597.982],[368.643,597.982],[538.004,597.982],[538.004,304.9],[463.485,304.9],[2.824,304.9],[117.989,138.82],[233.155,304.9],[348.32,138.82],[463.485,304.9],[463.485,138.82],[2.824,138.82],[117.989,-27.26],[233.155,138.82],[348.32,-27.26],[463.485,138.82],[463.485,-27.26],[2.824,-27.26],[117.989,-193.34],[233.155,-27.26],[348.32,-193.34],[463.485,-27.26],[463.485,-193.34],[2.824,-193.34],[117.989,-359.42],[233.155,-193.34],[348.32,-359.42],[463.485,-193.34],[463.485,-486.422],[348.32,-359.42],[233.155,-486.422],[117.989,-359.42],[2.824,-486.422],[2.824,-359.42],[233.155,-359.42],[233.155,-408.267],[233.155,-457.114],[233.155,-505.961],[233.155,-554.808]]</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="28" customHeight="1">
@@ -544,13 +544,13 @@
         <x:v>[[2,2],[5,2],[8,2],[11,2],[14,2],[18,2],[21,2],[24,2],[27,2],[31,2],[35,2],[39,2],[43,2],[47,2],[50,2],[54,2],[58,2],[62,2],[66,2]]</x:v>
       </x:c>
       <x:c r="C11" s="14" t="str">
-        <x:v>[[0,1000],[0,640],[0,500],[0,120],[53.256,104.584],[103.134,60.173],[120,0],[109.852,-53.373],[62.504,-94.346],[0,-120],[-64.544,-100.318],[-99.77,-56.581],[-120,0],[-106.474,58.564],[-68.148,101.627],[0,120],[-16.348,193.727],[-38.896,270.555],[-64.544,347.383],[-102.592,418.01],[-151.066,476.573],[-209.688,525.165],[-263.514,556.501],[-333.688,549.965],[-372.862,484.529],[-358.21,415.657],[-328.058,349.884],[-290.58,293.076],[-250.28,237.276],[-196.454,184.24],[-151.928,143.604],[-79.502,99.867],[-143.476,87.131],[-224.924,77.159],[-303.272,54.787],[-340,0],[-307.22,-60.587],[-228.594,-91.923],[-165.468,-92.259],[-102.342,-70.895],[-165.19,-130.468],[-218.738,-174.539],[-270.312,-236.875],[-312.586,-299.211],[-347.534,-371.183],[-344.434,-436.284],[-327.808,-492.421],[-283.282,-539.257],[-213.956,-530.293],[-169.43,-493.429],[-118.704,-431.765],[-82.352,-379.737],[-47.126,-305.674],[-18.1,-240.91],[-4.574,-169.947],[0,-120],[0,-119.99999999999983],[4.574000000000012,-169.9469999999999],[18.100000000000023,-240.9099999999999],[47.12600000000003,-305.67399999999986],[82.35199999999998,-379.73699999999985],[118.70400000000001,-431.7649999999999],[169.43,-493.42899999999986],[213.95599999999996,-530.293],[283.28199999999987,-539.2569999999998],[327.80800000000005,-492.42099999999994],[344.434,-436.284],[347.53400000000005,-371.1829999999999],[312.58599999999996,-299.2109999999999],[270.31200000000007,-236.8749999999999],[218.738,-174.53899999999987],[165.19,-130.46800000000002],[102.34199999999998,-70.89499999999998],[165.46800000000007,-92.25899999999979],[228.594,-91.92299999999983],[307.21999999999997,-60.58699999999976],[340.00000000000006,1.1368683772161603e-13],[303.272,54.78700000000015],[224.92399999999992,77.15900000000022],[143.476,87.1310000000002],[79.50199999999995,99.86700000000019],[151.92799999999994,143.60400000000027],[196.454,184.24000000000024],[250.28000000000003,237.27600000000018],[290.58,293.07600000000025],[328.05800000000005,349.8840000000001],[358.21,415.65700000000004],[372.86200000000014,484.52900000000034],[333.68799999999993,549.965],[263.51399999999995,556.5010000000001],[209.68800000000005,525.1650000000001],[151.0660000000001,476.5730000000002],[102.59199999999998,418.0100000000002],[64.54400000000004,347.38300000000004],[38.896000000000015,270.5550000000002],[16.348000000000013,193.7270000000001],[0,120.00000000000011],[-5.074,79.364],[-7.048,38.728]]</x:v>
+        <x:v>[[198.703,1002.033],[198.703,642.033],[198.703,502.033],[198.703,122.033],[232.894,106.617],[264.916,62.206],[275.744,2.033],[269.229,-51.34],[238.831,-92.313],[198.703,-117.967],[157.264,-98.285],[134.649,-54.548],[121.661,2.033],[130.344,60.597],[154.95,103.66],[198.703,122.033],[188.207,195.76],[173.731,272.588],[157.264,349.416],[132.837,420.043],[101.716,478.606],[64.079,527.198],[29.522,558.534],[-15.531,551.998],[-40.681,486.562],[-31.274,417.69],[-11.916,351.917],[12.145,295.109],[38.019,239.309],[72.576,186.273],[101.162,145.637],[147.661,101.9],[106.589,89.164],[54.298,79.192],[3.997,56.82],[-19.583,2.033],[1.462,-58.554],[51.941,-89.89],[92.469,-90.226],[132.997,-68.862],[92.648,-128.435],[58.269,-172.506],[25.158,-234.842],[-1.983,-297.178],[-24.42,-369.15],[-22.43,-434.251],[-11.756,-490.388],[16.831,-537.224],[61.339,-528.26],[89.926,-491.396],[122.493,-429.732],[145.831,-377.704],[168.447,-303.641],[187.082,-238.877],[195.766,-167.914],[198.703,-117.967],[198.703,-117.967],[201.639,-167.914],[210.323,-238.877],[228.958,-303.641],[251.574,-377.704],[274.912,-429.732],[307.479,-491.396],[336.066,-528.26],[380.574,-537.224],[409.161,-490.388],[419.835,-434.251],[421.825,-369.15],[399.388,-297.178],[372.247,-234.842],[339.136,-172.506],[304.757,-128.435],[264.408,-68.862],[304.936,-90.226],[345.464,-89.89],[395.943,-58.554],[416.988,2.033],[393.408,56.82],[343.107,79.192],[290.816,89.164],[249.744,101.9],[296.243,145.637],[324.829,186.273],[359.386,239.309],[385.26,295.109],[409.321,351.917],[428.679,417.69],[438.086,486.562],[412.936,551.998],[367.883,558.534],[333.326,527.198],[295.689,478.606],[264.568,420.043],[240.141,349.416],[223.674,272.588],[209.198,195.76],[198.703,122.033],[195.445,81.397],[194.178,40.761],[192.352,-606.218]]</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1ee833f63073449a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R21964b9604d94ddd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -688,7 +688,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f26cb625fa640e9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R60e34a5e1d3e4bf8"/>
   </x:tableParts>
 </x:worksheet>
 </file>